--- a/data/trans_dic/IP16A112_2023R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A112_2023R-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han consumido medicinas para el dolor y/o para bajar la fiebre</t>
+          <t>Menores que han consumido medicinas para el dolor y/o para bajar la fiebre (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>34,66; 68,93</t>
+          <t>35,47; 71,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,78; 57,97</t>
+          <t>29,45; 60,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35,68; 58,81</t>
+          <t>35,98; 59,37</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,94; 59,19</t>
+          <t>33,57; 59,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,94; 60,18</t>
+          <t>36,11; 59,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38,47; 56,66</t>
+          <t>37,44; 56,0</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46,95; 73,3</t>
+          <t>46,11; 73,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,42; 56,97</t>
+          <t>32,16; 58,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40,3; 60,68</t>
+          <t>41,12; 60,89</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,93; 41,59</t>
+          <t>8,2; 40,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,39; 53,77</t>
+          <t>30,1; 54,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,82; 42,22</t>
+          <t>16,68; 42,27</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>23,77; 49,62</t>
+          <t>24,25; 50,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37,26; 50,85</t>
+          <t>37,85; 51,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,87; 46,96</t>
+          <t>31,54; 47,59</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han consumido medicinas para el dolor y/o para bajar la fiebre (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>8629</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9659</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18288</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>5813; 11785</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6585; 13529</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13940; 23004</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>21716</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>23264</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>44980</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>15652; 27531</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>17687; 29078</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>35798; 53545</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>22793</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>20080</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>42873</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>17131; 27265</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14847; 26843</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>34262; 50731</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>18378</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27093</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>45471</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>6496; 31801</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>19626; 35321</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>24083; 61029</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>71517</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>80096</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>151613</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>43497; 90425</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>69163; 93943</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>114202; 172312</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A112_2023R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A112_2023R-Edad-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,47; 71,9</t>
+          <t>33,65; 69,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,45; 60,51</t>
+          <t>30,42; 60,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35,98; 59,37</t>
+          <t>36,07; 58,9</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,57; 59,05</t>
+          <t>33,82; 58,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,11; 59,36</t>
+          <t>35,16; 59,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,44; 56,0</t>
+          <t>37,98; 55,93</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46,11; 73,39</t>
+          <t>47,89; 73,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32,16; 58,14</t>
+          <t>30,25; 58,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41,12; 60,89</t>
+          <t>42,35; 60,88</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,2; 40,16</t>
+          <t>6,72; 39,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,1; 54,17</t>
+          <t>27,96; 53,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,68; 42,27</t>
+          <t>17,77; 43,14</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,25; 50,42</t>
+          <t>25,01; 50,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37,85; 51,42</t>
+          <t>37,19; 50,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,54; 47,59</t>
+          <t>32,59; 47,74</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5813; 11785</t>
+          <t>5516; 11457</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6585; 13529</t>
+          <t>6801; 13533</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13940; 23004</t>
+          <t>13977; 22822</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15652; 27531</t>
+          <t>15769; 27463</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17687; 29078</t>
+          <t>17222; 29298</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35798; 53545</t>
+          <t>36316; 53469</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17131; 27265</t>
+          <t>17791; 27379</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14847; 26843</t>
+          <t>13967; 26800</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34262; 50731</t>
+          <t>35288; 50726</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6496; 31801</t>
+          <t>5321; 31439</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19626; 35321</t>
+          <t>18229; 34592</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24083; 61029</t>
+          <t>25658; 62281</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>43497; 90425</t>
+          <t>44851; 90132</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>69163; 93943</t>
+          <t>67953; 92577</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>114202; 172312</t>
+          <t>118007; 172866</t>
         </is>
       </c>
     </row>
